--- a/measurements/33/Filled_2D_sections/coronal/week33_coronal_Batch_Allmarks.xlsx
+++ b/measurements/33/Filled_2D_sections/coronal/week33_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,122 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +616,76 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.770969660916122</v>
+        <v>2962.131519274376</v>
       </c>
       <c r="D2" t="n">
-        <v>18.51588686791862</v>
+        <v>361.5006483736492</v>
       </c>
       <c r="E2" t="n">
-        <v>12.63347925790926</v>
+        <v>246.6536426544189</v>
       </c>
       <c r="F2" t="n">
         <v>1.465620553920381</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2848367621115054</v>
+        <v>0.2848367621115055</v>
       </c>
       <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.451636904761905</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.66629464285714</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.997628348214285</v>
+      </c>
+      <c r="L2" t="n">
         <v>3</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.7006478658536586</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.956078506097561</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.8021468495934959</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>18.66629464285714</v>
+      </c>
+      <c r="N2" t="n">
+        <v>14.63727678571428</v>
+      </c>
+      <c r="O2" t="n">
+        <v>13.67931547619048</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.281994047619047</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6.19047619047619</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5.636625744047619</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.451636904761905</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>7.639961332540155</v>
+      <c r="AK2" s="2" t="n">
+        <v>2912.19387755102</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +696,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.822129684711482</v>
+        <v>2981.632653061224</v>
       </c>
       <c r="D3" t="n">
-        <v>17.80928780102148</v>
+        <v>347.705142781848</v>
       </c>
       <c r="E3" t="n">
-        <v>12.6251098731669</v>
+        <v>246.4902403808775</v>
       </c>
       <c r="F3" t="n">
         <v>1.41062438108938</v>
@@ -572,24 +715,60 @@
         <v>0.3099144110749263</v>
       </c>
       <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.979166666666667</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.89880952380952</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.160109747023808</v>
+      </c>
+      <c r="L3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.6966463414634146</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.9679878048780488</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.7882367886178862</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>18.89880952380952</v>
+      </c>
+      <c r="N3" t="n">
+        <v>13.66815476190476</v>
+      </c>
+      <c r="O3" t="n">
+        <v>13.60119047619048</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5.377604166666666</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4.348958333333333</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3.787202380952381</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.619791666666667</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.979166666666667</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>18.84572595692262</v>
+      <c r="AK3" s="2" t="n">
+        <v>367.9403639208703</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +779,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.870017846519929</v>
+        <v>2999.886621315192</v>
       </c>
       <c r="D4" t="n">
-        <v>17.94134180720259</v>
+        <v>350.283340045384</v>
       </c>
       <c r="E4" t="n">
-        <v>12.694095893604</v>
+        <v>247.8371103036971</v>
       </c>
       <c r="F4" t="n">
         <v>1.413361137144273</v>
@@ -619,24 +798,63 @@
         <v>0.3072385740803212</v>
       </c>
       <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.184895833333333</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.09784226190476</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.918526785714285</v>
+      </c>
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.6935975609756098</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.9781821646341464</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.8027502540650406</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>19.09784226190476</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14.37872023809524</v>
+      </c>
+      <c r="O4" t="n">
+        <v>13.54166666666667</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5.543154761904762</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.376860119047619</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3.757440476190476</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.184895833333333</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3.050595238095238</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.122395833333333</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>12.68535006976709</v>
+      <c r="AK4" s="2" t="n">
+        <v>247.6663585049765</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +865,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.894408090422368</v>
+        <v>3009.183673469387</v>
       </c>
       <c r="D5" t="n">
-        <v>19.27718450674197</v>
+        <v>376.3640784649622</v>
       </c>
       <c r="E5" t="n">
-        <v>12.64531538835386</v>
+        <v>246.8847290107182</v>
       </c>
       <c r="F5" t="n">
         <v>1.52445264627373</v>
@@ -666,23 +884,53 @@
         <v>0.2669575627383486</v>
       </c>
       <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.072172619047619</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.84858630952381</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.723420965608467</v>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.5796493902439025</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.9654153963414634</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.7359708460365854</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="n">
+        <v>11.31696428571428</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>18.84858630952381</v>
+      </c>
+      <c r="R5" t="n">
+        <v>14.36895461309524</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.072172619047619</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.236607142857143</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.406994047619047</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AK5" s="2" t="n">
         <v>1.48571844314757</v>
       </c>
     </row>
@@ -694,17 +942,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.922962522308151</v>
+        <v>3020.068027210884</v>
       </c>
       <c r="D6" t="n">
-        <v>19.23677346183032</v>
+        <v>375.5751009214492</v>
       </c>
       <c r="E6" t="n">
-        <v>12.62756121740109</v>
+        <v>246.5380999587831</v>
       </c>
       <c r="F6" t="n">
         <v>1.523395779330817</v>
@@ -713,23 +961,56 @@
         <v>0.2690500049443733</v>
       </c>
       <c r="H6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.209077380952381</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18.40401785714286</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.769311417748916</v>
+      </c>
+      <c r="L6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.5923208841463414</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.9426448170731707</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.7328267911585366</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="n">
+        <v>11.56436011904762</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>18.40401785714286</v>
+      </c>
+      <c r="R6" t="n">
+        <v>14.30757068452381</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.040178571428571</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.209077380952381</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.905505952380952</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.198660714285714</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AK6" s="2" t="n">
         <v>0.2708624338630755</v>
       </c>
     </row>
@@ -741,17 +1022,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.905413444378347</v>
+        <v>3013.378684807256</v>
       </c>
       <c r="D7" t="n">
-        <v>19.59599103287953</v>
+        <v>382.5883963562193</v>
       </c>
       <c r="E7" t="n">
-        <v>12.61082238104285</v>
+        <v>246.2112941060747</v>
       </c>
       <c r="F7" t="n">
         <v>1.553902706800239</v>
@@ -760,24 +1041,60 @@
         <v>0.2587021201402889</v>
       </c>
       <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.218377976190476</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.37611607142857</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.515997023809523</v>
+      </c>
+      <c r="L7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.6102324695121951</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.9412157012195123</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.7165110518292683</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="n">
+        <v>11.9140625</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>18.37611607142857</v>
+      </c>
+      <c r="R7" t="n">
+        <v>13.98902529761905</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.963541666666666</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4.376860119047619</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.218377976190476</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.732514880952381</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.21586681547619</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>3.85</v>
+      <c r="AK7" s="2" t="n">
+        <v>8.75</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1105,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.881915526472338</v>
+        <v>3004.421768707483</v>
       </c>
       <c r="D8" t="n">
-        <v>19.68416724263168</v>
+        <v>384.3099318799518</v>
       </c>
       <c r="E8" t="n">
-        <v>12.67634170520596</v>
+        <v>247.490480911164</v>
       </c>
       <c r="F8" t="n">
         <v>1.552827124764846</v>
@@ -807,24 +1124,57 @@
         <v>0.255627485176646</v>
       </c>
       <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.4609375</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.359375</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.053199404761903</v>
+      </c>
+      <c r="L8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.653296493902439</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.9403582317073171</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.736375762195122</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="n">
+        <v>12.75483630952381</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>18.359375</v>
+      </c>
+      <c r="R8" t="n">
+        <v>14.37686011904762</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.951636904761904</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4.877232142857142</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.628348214285714</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.4609375</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6044397865853659</v>
+      <c r="AK8" s="2" t="n">
+        <v>1.951915922619047</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1185,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.8837001784652</v>
+        <v>3005.102040816326</v>
       </c>
       <c r="D9" t="n">
-        <v>19.00614313672229</v>
+        <v>371.0723183836255</v>
       </c>
       <c r="E9" t="n">
-        <v>12.76553326699792</v>
+        <v>249.2318399747213</v>
       </c>
       <c r="F9" t="n">
         <v>1.488864016817683</v>
@@ -854,24 +1204,57 @@
         <v>0.2742533695826325</v>
       </c>
       <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.555803571428571</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18.36123511904762</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.942057291666666</v>
+      </c>
+      <c r="L9" t="n">
         <v>4</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.6290015243902439</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.940453506097561</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7339700838414634</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="n">
+        <v>12.28050595238095</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>18.36123511904762</v>
+      </c>
+      <c r="R9" t="n">
+        <v>14.32989211309524</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5.158110119047619</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.88578869047619</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.6171875</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.555803571428571</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.9543349847560976</v>
+      <c r="AK9" s="2" t="n">
+        <v>18.63225446428572</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1265,76 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.873884592504462</v>
+        <v>3001.360544217687</v>
       </c>
       <c r="D10" t="n">
-        <v>19.03226671567777</v>
+        <v>371.5823501632327</v>
       </c>
       <c r="E10" t="n">
-        <v>12.74287640757677</v>
+        <v>248.789491766975</v>
       </c>
       <c r="F10" t="n">
         <v>1.49356127352545</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2731604871969393</v>
+        <v>0.2731604871969392</v>
       </c>
       <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.371651785714286</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.728841145833334</v>
+      </c>
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.5936547256097561</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.951219512195122</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.7287538109756098</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="n">
+        <v>11.59040178571428</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="R10" t="n">
+        <v>14.22805059523809</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.776785714285714</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.894345238095238</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.875744047619047</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.371651785714286</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.7456189659552845</v>
+      <c r="AK10" s="2" t="n">
+        <v>8.298172033767736</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1345,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.858120166567519</v>
+        <v>2995.351473922902</v>
       </c>
       <c r="D11" t="n">
-        <v>18.5671187144954</v>
+        <v>362.5008891877674</v>
       </c>
       <c r="E11" t="n">
-        <v>12.83206792284803</v>
+        <v>250.530849922271</v>
       </c>
       <c r="F11" t="n">
         <v>1.446931143610601</v>
@@ -948,16 +1364,57 @@
         <v>0.2864438493765685</v>
       </c>
       <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.03125</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18.43377976190476</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.489350818452378</v>
+      </c>
+      <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.5989900914634146</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.9441692073170732</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.7315405868902439</v>
+      <c r="P11" t="n">
+        <v>11.69456845238095</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>18.43377976190476</v>
+      </c>
+      <c r="R11" t="n">
+        <v>14.28245907738095</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.389880952380953</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.234002976190476</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.129836309523809</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.03125</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1425,76 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.782272456870911</v>
+        <v>2966.439909297052</v>
       </c>
       <c r="D12" t="n">
-        <v>18.38628425539994</v>
+        <v>358.9703116530463</v>
       </c>
       <c r="E12" t="n">
-        <v>12.82369854392075</v>
+        <v>250.3674477622622</v>
       </c>
       <c r="F12" t="n">
-        <v>1.433773898569707</v>
+        <v>1.433773898569708</v>
       </c>
       <c r="G12" t="n">
         <v>0.2892866252715048</v>
       </c>
       <c r="H12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.313244047619047</v>
+      </c>
+      <c r="J12" t="n">
+        <v>18.42819940476191</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.561590608465607</v>
+      </c>
+      <c r="L12" t="n">
         <v>4</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.582983993902439</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.9438833841463415</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.7255383003048781</v>
+      <c r="P12" t="n">
+        <v>11.38206845238095</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>18.42819940476191</v>
+      </c>
+      <c r="R12" t="n">
+        <v>14.16527157738095</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.783482142857143</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.313244047619047</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.602306547619047</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.902436755952381</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>18.92764136904762</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1505,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.734681737061273</v>
+        <v>2948.299319727891</v>
       </c>
       <c r="D13" t="n">
-        <v>18.40302305977519</v>
+        <v>359.2971168813251</v>
       </c>
       <c r="E13" t="n">
-        <v>12.78328746411858</v>
+        <v>249.5784695375533</v>
       </c>
       <c r="F13" t="n">
         <v>1.439615835240398</v>
@@ -1026,16 +1524,54 @@
         <v>0.2869947628299854</v>
       </c>
       <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.789434523809524</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18.42819940476191</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.269624255952381</v>
+      </c>
+      <c r="L13" t="n">
         <v>4</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.572313262195122</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.9438833841463415</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.7161061356707317</v>
+      <c r="P13" t="n">
+        <v>11.17373511904762</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>18.42819940476191</v>
+      </c>
+      <c r="R13" t="n">
+        <v>13.98111979166667</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.789434523809524</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3.368675595238095</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.558128720238095</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>14.599609375</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1582,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.660618679357525</v>
+        <v>2920.068027210884</v>
       </c>
       <c r="D14" t="n">
-        <v>18.68488524018264</v>
+        <v>364.8001404035659</v>
       </c>
       <c r="E14" t="n">
-        <v>12.78328742922806</v>
+        <v>249.5784688563574</v>
       </c>
       <c r="F14" t="n">
         <v>1.461665111077844</v>
@@ -1065,16 +1601,54 @@
         <v>0.2757355989578983</v>
       </c>
       <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.293526785714286</v>
+      </c>
+      <c r="J14" t="n">
+        <v>18.88206845238095</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.796735491071429</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.5701219512195123</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.9671303353658537</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.753977705792683</v>
+      <c r="P14" t="n">
+        <v>11.13095238095238</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>18.88206845238095</v>
+      </c>
+      <c r="R14" t="n">
+        <v>14.72051711309524</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.293526785714286</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3.49516369047619</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.872953869047619</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>13.11383928571429</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1659,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.567816775728733</v>
+        <v>2884.69387755102</v>
       </c>
       <c r="D15" t="n">
-        <v>19.15941803048297</v>
+        <v>374.0648282141912</v>
       </c>
       <c r="E15" t="n">
-        <v>12.74879444808495</v>
+        <v>248.9050344626109</v>
       </c>
       <c r="F15" t="n">
         <v>1.502841551685774</v>
@@ -1104,16 +1678,57 @@
         <v>0.2590692372421262</v>
       </c>
       <c r="H15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.563244047619047</v>
+      </c>
+      <c r="J15" t="n">
+        <v>18.87276785714286</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9.209914434523808</v>
+      </c>
+      <c r="L15" t="n">
         <v>4</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.5890815548780488</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.9666539634146342</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.7587890625</v>
+      <c r="P15" t="n">
+        <v>11.50111607142857</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>18.87276785714286</v>
+      </c>
+      <c r="R15" t="n">
+        <v>14.814453125</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.66703869047619</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.162946428571428</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.028273809523809</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.563244047619047</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>11.52715773809524</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1739,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.479476502082094</v>
+        <v>2851.020408163265</v>
       </c>
       <c r="D16" t="n">
-        <v>19.53537443498286</v>
+        <v>381.4049294449034</v>
       </c>
       <c r="E16" t="n">
-        <v>12.8379859895241</v>
+        <v>250.6463931288038</v>
       </c>
       <c r="F16" t="n">
         <v>1.521685290116681</v>
@@ -1143,16 +1758,57 @@
         <v>0.2462847871544975</v>
       </c>
       <c r="H16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.526041666666667</v>
+      </c>
+      <c r="J16" t="n">
+        <v>18.88206845238095</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9.631696428571429</v>
+      </c>
+      <c r="L16" t="n">
         <v>4</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.5763147865853658</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.9671303353658537</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.750023818597561</v>
+      <c r="P16" t="n">
+        <v>11.25186011904762</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>18.88206845238095</v>
+      </c>
+      <c r="R16" t="n">
+        <v>14.64332217261905</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6.793154761904762</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6.184895833333333</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.976190476190476</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.526041666666667</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>18.55840773809524</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1819,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.410469958358121</v>
+        <v>2824.716553287982</v>
       </c>
       <c r="D17" t="n">
-        <v>19.08451390266418</v>
+        <v>372.6024142901102</v>
       </c>
       <c r="E17" t="n">
-        <v>12.71430144368149</v>
+        <v>248.2315996147337</v>
       </c>
       <c r="F17" t="n">
         <v>1.501027326369428</v>
@@ -1182,16 +1838,57 @@
         <v>0.255678029061337</v>
       </c>
       <c r="H17" t="n">
+        <v>8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.341889880952381</v>
+      </c>
+      <c r="J17" t="n">
+        <v>18.84858630952381</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9.260602678571429</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.5934641768292683</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.9654153963414634</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.7497141768292683</v>
+      <c r="P17" t="n">
+        <v>11.58668154761905</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>18.84858630952381</v>
+      </c>
+      <c r="R17" t="n">
+        <v>14.63727678571428</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7.118675595238095</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.262648809523809</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.8125</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.341889880952381</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>14.38337053571429</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1899,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.30696014277216</v>
+        <v>2785.260770975056</v>
       </c>
       <c r="D18" t="n">
-        <v>18.92980306613736</v>
+        <v>369.5818693864913</v>
       </c>
       <c r="E18" t="n">
-        <v>12.62857658979369</v>
+        <v>246.5579238959721</v>
       </c>
       <c r="F18" t="n">
         <v>1.498965693523707</v>
@@ -1221,16 +1918,60 @@
         <v>0.2562444163300262</v>
       </c>
       <c r="H18" t="n">
+        <v>9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.50297619047619</v>
+      </c>
+      <c r="J18" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="K18" t="n">
+        <v>8.476562499999998</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.5746951219512195</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.951219512195122</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.7360423018292683</v>
+      <c r="P18" t="n">
+        <v>11.22023809523809</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="R18" t="n">
+        <v>14.37034970238095</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6.46391369047619</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.904017857142857</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.7734375</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.163318452380952</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.50297619047619</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +1982,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.208506841165973</v>
+        <v>2747.732426303854</v>
       </c>
       <c r="D19" t="n">
-        <v>18.72529631126218</v>
+        <v>365.5891184579758</v>
       </c>
       <c r="E19" t="n">
-        <v>12.60837105134638</v>
+        <v>246.1634348120008</v>
       </c>
       <c r="F19" t="n">
         <v>1.485147941395855</v>
@@ -1260,16 +2001,63 @@
         <v>0.2583436442134986</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5512576219512195</v>
+        <v>1.768973214285714</v>
       </c>
       <c r="J19" t="n">
-        <v>0.975609756097561</v>
+        <v>19.04761904761905</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7318978658536586</v>
+        <v>8.325272817460318</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="N19" t="n">
+        <v>15.71428571428571</v>
+      </c>
+      <c r="O19" t="n">
+        <v>11.63318452380952</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>10.76264880952381</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.824032738095238</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.504092261904762</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.710193452380952</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.962425595238095</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.768973214285714</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>5.58896019345238</v>
       </c>
     </row>
     <row r="20">
@@ -1280,35 +2068,79 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.08923259964307</v>
+        <v>2702.267573696145</v>
       </c>
       <c r="D20" t="n">
-        <v>18.7263116778397</v>
+        <v>365.6089422816322</v>
       </c>
       <c r="E20" t="n">
-        <v>12.4930558611707</v>
+        <v>243.9120430038089</v>
       </c>
       <c r="F20" t="n">
         <v>1.498937640713062</v>
       </c>
       <c r="G20" t="n">
-        <v>0.254041457100717</v>
+        <v>0.2540414571007171</v>
       </c>
       <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.787574404761905</v>
+      </c>
+      <c r="J20" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.602492559523808</v>
+      </c>
+      <c r="L20" t="n">
         <v>4</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.5675495426829269</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.951219512195122</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.7346370045731707</v>
+      <c r="P20" t="n">
+        <v>11.08072916666667</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="R20" t="n">
+        <v>14.34291294642857</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5.37016369047619</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5.022321428571428</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.787574404761905</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.485119047619047</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.065197172619047</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>4.799783549783549</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2151,79 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.875669244497323</v>
+        <v>2620.861678004535</v>
       </c>
       <c r="D21" t="n">
-        <v>18.61344787260381</v>
+        <v>363.4054108460744</v>
       </c>
       <c r="E21" t="n">
-        <v>12.43243926036649</v>
+        <v>242.7285760357266</v>
       </c>
       <c r="F21" t="n">
         <v>1.497167810981537</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2493854926773685</v>
+        <v>0.2493854926773686</v>
       </c>
       <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.616443452380952</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18.09523809523809</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.530505952380952</v>
+      </c>
+      <c r="L21" t="n">
         <v>4</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.5629763719512195</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.926829268292683</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.7465701219512195</v>
+      <c r="P21" t="n">
+        <v>10.99144345238095</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>18.09523809523809</v>
+      </c>
+      <c r="R21" t="n">
+        <v>14.57589285714286</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.263392857142857</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.833705357142857</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.616443452380952</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.372395833333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.226097470238095</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>4.349578373015873</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2233,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>4.281994047619047</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2255,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>6.19047619047619</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2272,120 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>5.636625744047619</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>2.83600514069264</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>2.402901785714286</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>2.003348214285714</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>1.609416335978836</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>3.02765376984127</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>2.285414599867725</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/33/Filled_2D_sections/coronal/week33_coronal_Batch_Allmarks.xlsx
+++ b/measurements/33/Filled_2D_sections/coronal/week33_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2391,4 +2597,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week33_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2912.19387755102</v>
+      </c>
+      <c r="D10" t="n">
+        <v>118.5112889575344</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2620.861678004535</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3020.068027210884</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>367.9403639208703</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.9125984693448</v>
+      </c>
+      <c r="E11" t="n">
+        <v>347.705142781848</v>
+      </c>
+      <c r="F11" t="n">
+        <v>384.3099318799518</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.48571844314757</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.04144250772574749</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.41062438108938</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.553902706800239</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2708624338630755</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01837246210831426</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2462847871544975</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3099144110749263</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>11</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0153.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0154.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0156.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0158.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0159.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0161.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0162.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>9</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0163.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0164.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.9665456669582609</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4103913408340616</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.080935267549162</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.208522368758425</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>76</v>
+      </c>
+      <c r="C48" t="n">
+        <v>14.56710624216792</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.651692656225455</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10.99144345238095</v>
+      </c>
+      <c r="F48" t="n">
+        <v>19.09784226190476</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>34</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.229888830532213</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.359999254831075</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.757440476190476</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10.76264880952381</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>65</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.374170100732601</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5517307534376003</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.184895833333333</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.619791666666667</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>